--- a/CRONOGRAMA/Springs.xlsx
+++ b/CRONOGRAMA/Springs.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\TALLER DE PROYECTOS\PROYECTO-REPOSITORIO\taller-proyectos-1\CRONOGRAMA\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE89A467-9F8C-44AA-BA3A-B4C4F41E9BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Spring 1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Spring 2" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Spring 3" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Spring 4" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Spring 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Spring 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Spring 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Spring 4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -25,23 +40,20 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="3">
   <si>
-    <t xml:space="preserve">Tiempo</t>
+    <t>Tiempo</t>
   </si>
   <si>
-    <t xml:space="preserve">Actividad</t>
+    <t>Actividad</t>
   </si>
   <si>
-    <t xml:space="preserve">Avance</t>
+    <t>Avance</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -51,37 +63,10 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF595959"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -99,148 +84,117 @@
     </fill>
   </fills>
   <borders count="7">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -299,18 +253,37 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -329,10 +302,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="156082"/>
-            </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="156082"/>
               </a:solidFill>
@@ -349,12 +319,19 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -362,6 +339,7 @@
                     <a:latin typeface="Aptos Narrow"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-PE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -370,27 +348,29 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="28440" cap="rnd">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Spring 1'!$A$2:$A$7</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -402,7 +382,7 @@
                   <c:v>12.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.2</c:v>
+                  <c:v>19.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>25.6</c:v>
@@ -410,8 +390,8 @@
                 <c:pt idx="5">
                   <c:v>32</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -441,6 +421,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E7BC-4141-90ED-368A1630D3AA}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -457,12 +442,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="e97132"/>
-            </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="e97132"/>
+                <a:srgbClr val="E97132"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -472,17 +454,24 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="e97132"/>
+                <a:srgbClr val="E97132"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -490,6 +479,7 @@
                     <a:latin typeface="Aptos Narrow"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-PE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -498,27 +488,29 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="28440" cap="rnd">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Spring 1'!$A$2:$A$7</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -530,7 +522,7 @@
                   <c:v>12.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.2</c:v>
+                  <c:v>19.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>25.6</c:v>
@@ -538,8 +530,8 @@
                 <c:pt idx="5">
                   <c:v>32</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -569,7 +561,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E7BC-4141-90ED-368A1630D3AA}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -578,6 +583,7 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="24060554"/>
         <c:axId val="7444029"/>
       </c:lineChart>
@@ -595,13 +601,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" lang="es-PE" sz="1000" strike="noStrike" u="none">
+                  <a:rPr lang="es-PE" sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="595959"/>
                     </a:solidFill>
@@ -628,7 +634,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="d9d9d9"/>
+              <a:srgbClr val="D9D9D9"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -638,7 +644,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+              <a:defRPr sz="900" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
@@ -646,6 +652,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="7444029"/>
@@ -666,7 +673,7 @@
           <c:spPr>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="d9d9d9"/>
+                <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -679,13 +686,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" lang="es-PE" sz="1000" strike="noStrike" u="none">
+                  <a:rPr lang="es-PE" sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="595959"/>
                     </a:solidFill>
@@ -719,7 +726,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+              <a:defRPr sz="900" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
@@ -727,6 +734,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="24060554"/>
@@ -754,7 +762,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+            <a:defRPr sz="900" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="595959"/>
               </a:solidFill>
@@ -762,33 +770,43 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -807,10 +825,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="156082"/>
-            </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="156082"/>
               </a:solidFill>
@@ -827,12 +842,19 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -840,6 +862,7 @@
                     <a:latin typeface="Aptos Narrow"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-PE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -848,27 +871,29 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="28440" cap="rnd">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Spring 2'!$A$2:$A$7</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -880,7 +905,7 @@
                   <c:v>12.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.2</c:v>
+                  <c:v>19.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>25.6</c:v>
@@ -888,8 +913,8 @@
                 <c:pt idx="5">
                   <c:v>32</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -919,6 +944,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8018-4DB4-872F-9985B9D91FA9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -935,12 +965,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="e97132"/>
-            </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="e97132"/>
+                <a:srgbClr val="E97132"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -950,17 +977,24 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="e97132"/>
+                <a:srgbClr val="E97132"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -968,6 +1002,7 @@
                     <a:latin typeface="Aptos Narrow"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-PE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -976,27 +1011,29 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="28440" cap="rnd">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Spring 2'!$A$2:$A$7</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1008,7 +1045,7 @@
                   <c:v>12.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.2</c:v>
+                  <c:v>19.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>25.6</c:v>
@@ -1016,8 +1053,8 @@
                 <c:pt idx="5">
                   <c:v>32</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1047,7 +1084,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8018-4DB4-872F-9985B9D91FA9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -1056,6 +1106,7 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="15669978"/>
         <c:axId val="68179411"/>
       </c:lineChart>
@@ -1073,13 +1124,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" lang="es-PE" sz="1000" strike="noStrike" u="none">
+                  <a:rPr lang="es-PE" sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="595959"/>
                     </a:solidFill>
@@ -1106,7 +1157,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="d9d9d9"/>
+              <a:srgbClr val="D9D9D9"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1116,7 +1167,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+              <a:defRPr sz="900" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
@@ -1124,6 +1175,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="68179411"/>
@@ -1144,7 +1196,7 @@
           <c:spPr>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="d9d9d9"/>
+                <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1157,13 +1209,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" lang="es-PE" sz="1000" strike="noStrike" u="none">
+                  <a:rPr lang="es-PE" sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="595959"/>
                     </a:solidFill>
@@ -1197,7 +1249,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+              <a:defRPr sz="900" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
@@ -1205,6 +1257,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="15669978"/>
@@ -1232,7 +1285,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+            <a:defRPr sz="900" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="595959"/>
               </a:solidFill>
@@ -1240,33 +1293,43 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -1285,10 +1348,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="156082"/>
-            </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="156082"/>
               </a:solidFill>
@@ -1305,12 +1365,19 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1318,6 +1385,7 @@
                     <a:latin typeface="Aptos Narrow"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-PE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -1326,28 +1394,30 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="28440" cap="rnd">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
-              <c:f>'Spring 3'!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
+            <c:numRef>
+              <c:f>'Spring 3'!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1363,15 +1433,15 @@
                 <c:pt idx="4">
                   <c:v>32</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Spring 3'!$B$2:$B$6</c:f>
+              <c:f>'Spring 3'!$B$2:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -1391,6 +1461,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FF15-4128-AEB5-FD191F773BA5}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1407,12 +1482,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="e97132"/>
-            </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="e97132"/>
+                <a:srgbClr val="E97132"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1422,17 +1494,24 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="e97132"/>
+                <a:srgbClr val="E97132"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1440,6 +1519,7 @@
                     <a:latin typeface="Aptos Narrow"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-PE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -1448,28 +1528,30 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="28440" cap="rnd">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
-              <c:f>'Spring 3'!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
+            <c:numRef>
+              <c:f>'Spring 3'!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1485,20 +1567,48 @@
                 <c:pt idx="4">
                   <c:v>32</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Spring 3'!$C$2:$C$6</c:f>
+              <c:f>'Spring 3'!$C$2:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FF15-4128-AEB5-FD191F773BA5}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -1507,6 +1617,7 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="41514734"/>
         <c:axId val="96301378"/>
       </c:lineChart>
@@ -1524,13 +1635,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" lang="es-PE" sz="1000" strike="noStrike" u="none">
+                  <a:rPr lang="es-PE" sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="595959"/>
                     </a:solidFill>
@@ -1557,7 +1668,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="d9d9d9"/>
+              <a:srgbClr val="D9D9D9"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1567,7 +1678,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+              <a:defRPr sz="900" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
@@ -1575,6 +1686,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="96301378"/>
@@ -1595,7 +1707,7 @@
           <c:spPr>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="d9d9d9"/>
+                <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1608,13 +1720,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" lang="es-PE" sz="1000" strike="noStrike" u="none">
+                  <a:rPr lang="es-PE" sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="595959"/>
                     </a:solidFill>
@@ -1648,7 +1760,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+              <a:defRPr sz="900" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
@@ -1656,6 +1768,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="41514734"/>
@@ -1683,7 +1796,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+            <a:defRPr sz="900" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="595959"/>
               </a:solidFill>
@@ -1691,33 +1804,43 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -1736,10 +1859,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="156082"/>
-            </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="156082"/>
               </a:solidFill>
@@ -1756,12 +1876,19 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1769,6 +1896,7 @@
                     <a:latin typeface="Aptos Narrow"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-PE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -1777,27 +1905,29 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="28440" cap="rnd">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Spring 4'!$A$2:$A$5</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1811,8 +1941,8 @@
                 <c:pt idx="3">
                   <c:v>32</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1836,6 +1966,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3FE9-4F01-959E-4D03A6C88150}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1852,12 +1987,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="e97132"/>
-            </a:solidFill>
-            <a:ln cap="rnd" w="28440">
+            <a:ln w="28440" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="e97132"/>
+                <a:srgbClr val="E97132"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1867,17 +1999,24 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="e97132"/>
+                <a:srgbClr val="E97132"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1885,6 +2024,7 @@
                     <a:latin typeface="Aptos Narrow"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-PE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="r"/>
@@ -1893,27 +2033,29 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln cap="rnd" w="28440">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="28440" cap="rnd">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Spring 4'!$A$2:$A$5</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1927,8 +2069,8 @@
                 <c:pt idx="3">
                   <c:v>32</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1936,11 +2078,33 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3FE9-4F01-959E-4D03A6C88150}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -1949,6 +2113,7 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="60665670"/>
         <c:axId val="85763478"/>
       </c:lineChart>
@@ -1966,13 +2131,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" lang="es-PE" sz="1000" strike="noStrike" u="none">
+                  <a:rPr lang="es-PE" sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="595959"/>
                     </a:solidFill>
@@ -1999,7 +2164,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="d9d9d9"/>
+              <a:srgbClr val="D9D9D9"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2009,7 +2174,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+              <a:defRPr sz="900" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
@@ -2017,6 +2182,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="85763478"/>
@@ -2037,7 +2203,7 @@
           <c:spPr>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="d9d9d9"/>
+                <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2050,13 +2216,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" lang="es-PE" sz="1000" strike="noStrike" u="none">
+                  <a:rPr lang="es-PE" sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="595959"/>
                     </a:solidFill>
@@ -2090,7 +2256,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+              <a:defRPr sz="900" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="595959"/>
                 </a:solidFill>
@@ -2098,6 +2264,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="60665670"/>
@@ -2125,7 +2292,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="900" strike="noStrike" u="none">
+            <a:defRPr sz="900" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="595959"/>
               </a:solidFill>
@@ -2133,28 +2300,35 @@
               <a:latin typeface="Aptos Narrow"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -2168,14 +2342,20 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>165960</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Gráfico 1"/>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3927600" y="662040"/>
-        <a:ext cx="5618880" cy="2742480"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2189,7 +2369,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -2203,14 +2383,20 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>165960</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Gráfico 1"/>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3927600" y="662040"/>
-        <a:ext cx="5618880" cy="2742480"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2224,7 +2410,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -2238,14 +2424,20 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>165960</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1"/>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3927600" y="662040"/>
-        <a:ext cx="5618880" cy="2552040"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2259,7 +2451,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -2273,14 +2465,20 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>165960</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 1"/>
+        <xdr:cNvPr id="3" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3927600" y="662040"/>
-        <a:ext cx="5618880" cy="2361600"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2294,98 +2492,102 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:C7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:C7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:C7" totalsRowShown="0">
+  <autoFilter ref="A1:C7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Tiempo"/>
-    <tableColumn id="2" name="Actividad"/>
-    <tableColumn id="3" name="Avance"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tiempo"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Actividad"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Avance"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla13" displayName="Tabla13" ref="A1:C7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:C7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla13" displayName="Tabla13" ref="A1:C7" totalsRowShown="0">
+  <autoFilter ref="A1:C7" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Tiempo"/>
-    <tableColumn id="2" name="Actividad"/>
-    <tableColumn id="3" name="Avance"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Tiempo"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Actividad"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Avance"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla134" displayName="Tabla134" ref="A1:C6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:C6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabla134" displayName="Tabla134" ref="A1:C7" totalsRowShown="0">
+  <autoFilter ref="A1:C7" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Tiempo"/>
-    <tableColumn id="2" name="Actividad"/>
-    <tableColumn id="3" name="Avance"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Tiempo"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Actividad"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Avance"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabla1345" displayName="Tabla1345" ref="A1:C5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:C5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabla1345" displayName="Tabla1345" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Tiempo"/>
-    <tableColumn id="2" name="Actividad"/>
-    <tableColumn id="3" name="Avance"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Tiempo"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Actividad"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Avance"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0e2841"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="e97132"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196b24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="a02b93"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4ea72e"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607d"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -2417,7 +2619,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2441,7 +2643,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2501,23 +2703,22 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2528,104 +2729,96 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:4">
+      <c r="A2" s="3">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="4">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="5">
         <v>6.4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
-        <f aca="false">A2+$D$2</f>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3">
+        <f>A2+$D$2</f>
         <v>6.4</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="4">
         <v>4</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3">
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
-        <f aca="false">A3+$D$2</f>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3">
+        <f>A3+$D$2</f>
         <v>12.8</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="4">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
-        <f aca="false">A4+$D$2</f>
-        <v>19.2</v>
-      </c>
-      <c r="B5" s="4" t="n">
+    <row r="5" spans="1:4">
+      <c r="A5" s="3">
+        <f>A4+$D$2</f>
+        <v>19.200000000000003</v>
+      </c>
+      <c r="B5" s="4">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
-        <f aca="false">A5+$D$2</f>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3">
+        <f>A5+$D$2</f>
         <v>25.6</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
-        <f aca="false">A6+$D$2</f>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3">
+        <f>A6+$D$2</f>
         <v>32</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="6">
         <v>0</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
-  <tableParts>
+  <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2636,104 +2829,96 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="n">
+    <row r="2" spans="1:4">
+      <c r="A2" s="7">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="7">
         <v>5</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="8">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="5">
         <v>6.4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="n">
-        <f aca="false">A2+$D$2</f>
+    <row r="3" spans="1:4">
+      <c r="A3" s="7">
+        <f>A2+$D$2</f>
         <v>6.4</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="7">
         <v>4</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="n">
-        <f aca="false">A3+$D$2</f>
+    <row r="4" spans="1:4">
+      <c r="A4" s="7">
+        <f>A3+$D$2</f>
         <v>12.8</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="7">
         <v>3</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="n">
-        <f aca="false">A4+$D$2</f>
-        <v>19.2</v>
-      </c>
-      <c r="B5" s="8" t="n">
+    <row r="5" spans="1:4">
+      <c r="A5" s="7">
+        <f>A4+$D$2</f>
+        <v>19.200000000000003</v>
+      </c>
+      <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
-        <f aca="false">A5+$D$2</f>
+    <row r="6" spans="1:4">
+      <c r="A6" s="7">
+        <f>A5+$D$2</f>
         <v>25.6</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="7">
         <v>1</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
-        <f aca="false">A6+$D$2</f>
+    <row r="7" spans="1:4">
+      <c r="A7" s="7">
+        <f>A6+$D$2</f>
         <v>32</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="7">
         <v>0</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
-  <tableParts>
+  <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2744,73 +2929,80 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:4">
+      <c r="A2" s="3">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="4">
         <v>4</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5">
         <v>6.4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" spans="1:4">
+      <c r="A3" s="3">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="4">
         <v>3</v>
       </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:4">
+      <c r="A4" s="3">
         <v>16</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:4">
+      <c r="A5" s="3">
         <v>24</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="4">
         <v>1</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+    <row r="6" spans="1:4">
+      <c r="A6" s="3">
         <v>32</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
-  <tableParts>
+  <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2821,51 +3013,55 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:4">
+      <c r="A2" s="3">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="4">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5">
         <v>6.4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" spans="1:4">
+      <c r="A3" s="3">
         <v>10.6</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="4">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:4">
+      <c r="A4" s="3">
         <v>21.26</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="4">
         <v>1</v>
       </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:4">
+      <c r="A5" s="3">
         <v>32</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
-  <tableParts>
+  <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>

--- a/CRONOGRAMA/Springs.xlsx
+++ b/CRONOGRAMA/Springs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\TALLER DE PROYECTOS\PROYECTO-REPOSITORIO\taller-proyectos-1\CRONOGRAMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE89A467-9F8C-44AA-BA3A-B4C4F41E9BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABABB19-116D-44B8-94AF-B45659AD00A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1925,10 +1925,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Spring 4'!$A$2:$A$5</c:f>
+              <c:f>'Spring 4'!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1946,10 +1946,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Spring 4'!$B$2:$B$5</c:f>
+              <c:f>'Spring 4'!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -2053,10 +2053,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Spring 4'!$A$2:$A$5</c:f>
+              <c:f>'Spring 4'!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2074,10 +2074,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Spring 4'!$C$2:$C$5</c:f>
+              <c:f>'Spring 4'!$C$2:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -2086,6 +2086,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2528,8 +2531,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabla1345" displayName="Tabla1345" ref="A1:C5" totalsRowShown="0">
-  <autoFilter ref="A1:C5" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabla1345" displayName="Tabla1345" ref="A1:C6" totalsRowShown="0">
+  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Tiempo"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Actividad"/>
@@ -3056,6 +3059,9 @@
       <c r="B5" s="4">
         <v>0</v>
       </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
